--- a/ValueSet-medication-level.xlsx
+++ b/ValueSet-medication-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medication-level.xlsx
+++ b/ValueSet-medication-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medication-level.xlsx
+++ b/ValueSet-medication-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
